--- a/data/availability/projects/sodic/karmell.xlsx
+++ b/data/availability/projects/sodic/karmell.xlsx
@@ -1159,7 +1159,6 @@
       <c r="G2" t="n">
         <v>157</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1216,7 +1215,6 @@
       <c r="G3" t="n">
         <v>122</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1273,7 +1271,6 @@
       <c r="G4" t="n">
         <v>157</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1513,7 +1510,6 @@
       <c r="G8" t="n">
         <v>159</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1570,7 +1566,6 @@
       <c r="G9" t="n">
         <v>159</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1627,7 +1622,6 @@
       <c r="G10" t="n">
         <v>159</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1684,7 +1678,6 @@
       <c r="G11" t="n">
         <v>159</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1741,7 +1734,6 @@
       <c r="G12" t="n">
         <v>159</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1981,7 +1973,6 @@
       <c r="G16" t="n">
         <v>122</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2038,7 +2029,6 @@
       <c r="G17" t="n">
         <v>157</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2095,7 +2085,6 @@
       <c r="G18" t="n">
         <v>157</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2396,7 +2385,6 @@
       <c r="G23" t="n">
         <v>159</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2453,7 +2441,6 @@
       <c r="G24" t="n">
         <v>159</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2510,7 +2497,6 @@
       <c r="G25" t="n">
         <v>82</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2567,7 +2553,6 @@
       <c r="G26" t="n">
         <v>124</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2624,7 +2609,6 @@
       <c r="G27" t="n">
         <v>159</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2681,7 +2665,6 @@
       <c r="G28" t="n">
         <v>159</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2738,7 +2721,6 @@
       <c r="G29" t="n">
         <v>159</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2917,7 +2899,6 @@
       <c r="G32" t="n">
         <v>159</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2974,7 +2955,6 @@
       <c r="G33" t="n">
         <v>159</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3031,7 +3011,6 @@
       <c r="G34" t="n">
         <v>159</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3271,7 +3250,6 @@
       <c r="G38" t="n">
         <v>159</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3328,7 +3306,6 @@
       <c r="G39" t="n">
         <v>159</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3385,7 +3362,6 @@
       <c r="G40" t="n">
         <v>124</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3442,7 +3418,6 @@
       <c r="G41" t="n">
         <v>159</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3499,7 +3474,6 @@
       <c r="G42" t="n">
         <v>159</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3556,7 +3530,6 @@
       <c r="G43" t="n">
         <v>159</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3613,7 +3586,6 @@
       <c r="G44" t="n">
         <v>159</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4402,7 +4374,6 @@
       <c r="G57" t="n">
         <v>159</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4703,7 +4674,6 @@
       <c r="G62" t="n">
         <v>157</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5126,7 +5096,6 @@
       <c r="G69" t="n">
         <v>122</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5305,7 +5274,6 @@
       <c r="G72" t="n">
         <v>159</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5362,7 +5330,6 @@
       <c r="G73" t="n">
         <v>159</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5602,7 +5569,6 @@
       <c r="G77" t="n">
         <v>157</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5659,7 +5625,6 @@
       <c r="G78" t="n">
         <v>157</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5777,7 +5742,6 @@
       <c r="G80" t="n">
         <v>157</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5834,7 +5798,6 @@
       <c r="G81" t="n">
         <v>157</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5891,7 +5854,6 @@
       <c r="G82" t="n">
         <v>157</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6070,7 +6032,6 @@
       <c r="G85" t="n">
         <v>124</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6127,7 +6088,6 @@
       <c r="G86" t="n">
         <v>159</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6184,7 +6144,6 @@
       <c r="G87" t="n">
         <v>124</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6241,7 +6200,6 @@
       <c r="G88" t="n">
         <v>159</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6298,7 +6256,6 @@
       <c r="G89" t="n">
         <v>159</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6355,7 +6312,6 @@
       <c r="G90" t="n">
         <v>159</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6412,7 +6368,6 @@
       <c r="G91" t="n">
         <v>159</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6713,7 +6668,6 @@
       <c r="G96" t="n">
         <v>157</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6770,7 +6724,6 @@
       <c r="G97" t="n">
         <v>157</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6827,7 +6780,6 @@
       <c r="G98" t="n">
         <v>122</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6884,7 +6836,6 @@
       <c r="G99" t="n">
         <v>122</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6941,7 +6892,6 @@
       <c r="G100" t="n">
         <v>157</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6998,7 +6948,6 @@
       <c r="G101" t="n">
         <v>157</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7055,7 +7004,6 @@
       <c r="G102" t="n">
         <v>157</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7112,7 +7060,6 @@
       <c r="G103" t="n">
         <v>157</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7169,7 +7116,6 @@
       <c r="G104" t="n">
         <v>122</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7470,7 +7416,6 @@
       <c r="G109" t="n">
         <v>82</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7527,7 +7472,6 @@
       <c r="G110" t="n">
         <v>124</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7584,7 +7528,6 @@
       <c r="G111" t="n">
         <v>159</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7641,7 +7584,6 @@
       <c r="G112" t="n">
         <v>159</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7698,7 +7640,6 @@
       <c r="G113" t="n">
         <v>82</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7755,7 +7696,6 @@
       <c r="G114" t="n">
         <v>124</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7812,7 +7752,6 @@
       <c r="G115" t="n">
         <v>159</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7869,7 +7808,6 @@
       <c r="G116" t="n">
         <v>159</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7926,7 +7864,6 @@
       <c r="G117" t="n">
         <v>82</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7983,7 +7920,6 @@
       <c r="G118" t="n">
         <v>124</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8040,7 +7976,6 @@
       <c r="G119" t="n">
         <v>159</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8097,7 +8032,6 @@
       <c r="G120" t="n">
         <v>159</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8398,7 +8332,6 @@
       <c r="G125" t="n">
         <v>82</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8455,7 +8388,6 @@
       <c r="G126" t="n">
         <v>124</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8512,7 +8444,6 @@
       <c r="G127" t="n">
         <v>159</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8569,7 +8500,6 @@
       <c r="G128" t="n">
         <v>159</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8626,7 +8556,6 @@
       <c r="G129" t="n">
         <v>82</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8683,7 +8612,6 @@
       <c r="G130" t="n">
         <v>124</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8740,7 +8668,6 @@
       <c r="G131" t="n">
         <v>159</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8797,7 +8724,6 @@
       <c r="G132" t="n">
         <v>159</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8854,7 +8780,6 @@
       <c r="G133" t="n">
         <v>82</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8911,7 +8836,6 @@
       <c r="G134" t="n">
         <v>124</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8968,7 +8892,6 @@
       <c r="G135" t="n">
         <v>159</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9025,7 +8948,6 @@
       <c r="G136" t="n">
         <v>159</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9936,7 +9858,6 @@
       <c r="G151" t="n">
         <v>82</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9993,7 +9914,6 @@
       <c r="G152" t="n">
         <v>159</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10050,7 +9970,6 @@
       <c r="G153" t="n">
         <v>82</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10107,7 +10026,6 @@
       <c r="G154" t="n">
         <v>159</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10164,7 +10082,6 @@
       <c r="G155" t="n">
         <v>82</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10221,7 +10138,6 @@
       <c r="G156" t="n">
         <v>124</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10278,7 +10194,6 @@
       <c r="G157" t="n">
         <v>159</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11982,7 +11897,6 @@
       <c r="G185" t="n">
         <v>159</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12039,7 +11953,6 @@
       <c r="G186" t="n">
         <v>159</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12218,7 +12131,6 @@
       <c r="G189" t="n">
         <v>159</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12275,7 +12187,6 @@
       <c r="G190" t="n">
         <v>159</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12332,7 +12243,6 @@
       <c r="G191" t="n">
         <v>82</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12389,7 +12299,6 @@
       <c r="G192" t="n">
         <v>159</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12629,7 +12538,6 @@
       <c r="G196" t="n">
         <v>159</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12686,7 +12594,6 @@
       <c r="G197" t="n">
         <v>159</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12804,7 +12711,6 @@
       <c r="G199" t="n">
         <v>159</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12861,7 +12767,6 @@
       <c r="G200" t="n">
         <v>159</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14016,7 +13921,6 @@
       <c r="G219" t="n">
         <v>214</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14439,7 +14343,6 @@
       <c r="G226" t="n">
         <v>214</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14801,14 +14704,13 @@
       <c r="G232" t="n">
         <v>120</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
         </is>
       </c>
       <c r="J232" t="n">
-        <v>4</v>
+        <v>46584000</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>

--- a/data/availability/projects/sodic/karmell.xlsx
+++ b/data/availability/projects/sodic/karmell.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for karmell</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
